--- a/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
+++ b/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B413673-8A27-4913-AF37-FEA0177D78D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDA599B-A755-40F7-B6B6-BC2AD48B2C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
   <si>
     <t>Diese Sprache leitet die Sprache der Hölle weiter, da die Seelenbändiger diese gesprochen hatten, wie sie zusammen in einem Stamm gelebt hatten. Die späteren Nationen geführt durch die Bändiger entickelten die Sprachen weiter, die von Naitro'Nai wurde marziallischer, vorallem in der Hölle, als sich Bedeutungen start änderten.</t>
   </si>
@@ -271,6 +271,114 @@
   </si>
   <si>
     <t>Het</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Half</t>
+  </si>
+  <si>
+    <t>aril</t>
+  </si>
+  <si>
+    <t>Knowldge</t>
+  </si>
+  <si>
+    <t>Fury</t>
+  </si>
+  <si>
+    <t>Kekvar</t>
+  </si>
+  <si>
+    <t>Uncover</t>
+  </si>
+  <si>
+    <t>akliir</t>
+  </si>
+  <si>
+    <t>Miakliir</t>
+  </si>
+  <si>
+    <t>Dil</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>Air</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Metal</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Mind</t>
+  </si>
+  <si>
+    <t>Loss</t>
+  </si>
+  <si>
+    <t>Ker</t>
+  </si>
+  <si>
+    <t>Vra</t>
+  </si>
+  <si>
+    <t>Shi</t>
+  </si>
+  <si>
+    <t>Asht</t>
+  </si>
+  <si>
+    <t>Rui</t>
+  </si>
+  <si>
+    <t>Vao</t>
+  </si>
+  <si>
+    <t>Mish</t>
+  </si>
+  <si>
+    <t>Tsho</t>
+  </si>
+  <si>
+    <t>Tri</t>
+  </si>
+  <si>
+    <t>Aik</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Treahr</t>
+  </si>
+  <si>
+    <t>Rin</t>
+  </si>
+  <si>
+    <t>Binder</t>
+  </si>
+  <si>
+    <t>Orin</t>
   </si>
 </sst>
 </file>
@@ -588,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -650,10 +758,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -666,10 +774,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -958,6 +1066,150 @@
       </c>
       <c r="B48">
         <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>104</v>
+      </c>
+      <c r="B63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>117</v>
+      </c>
+      <c r="B66" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
+++ b/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDA599B-A755-40F7-B6B6-BC2AD48B2C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B2ADC-62D0-43E8-985A-43CBB9A5F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
   <si>
     <t>Diese Sprache leitet die Sprache der Hölle weiter, da die Seelenbändiger diese gesprochen hatten, wie sie zusammen in einem Stamm gelebt hatten. Die späteren Nationen geführt durch die Bändiger entickelten die Sprachen weiter, die von Naitro'Nai wurde marziallischer, vorallem in der Hölle, als sich Bedeutungen start änderten.</t>
   </si>
@@ -379,6 +379,42 @@
   </si>
   <si>
     <t>Orin</t>
+  </si>
+  <si>
+    <t>Plague</t>
+  </si>
+  <si>
+    <t>Shaik</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Moon</t>
+  </si>
+  <si>
+    <t>Dilarii</t>
+  </si>
+  <si>
+    <t>Darkness</t>
+  </si>
+  <si>
+    <t>Trelar</t>
+  </si>
+  <si>
+    <t>Tre</t>
+  </si>
+  <si>
+    <t>Spike</t>
+  </si>
+  <si>
+    <t>Meridor</t>
+  </si>
+  <si>
+    <t>Sorii</t>
+  </si>
+  <si>
+    <t>Wheat</t>
   </si>
 </sst>
 </file>
@@ -696,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1212,6 +1248,54 @@
         <v>116</v>
       </c>
     </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>122</v>
+      </c>
+      <c r="B68" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
+++ b/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B2ADC-62D0-43E8-985A-43CBB9A5F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C641AC3F-C8E7-4B03-B6E1-B292EEF31CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="132">
   <si>
     <t>Diese Sprache leitet die Sprache der Hölle weiter, da die Seelenbändiger diese gesprochen hatten, wie sie zusammen in einem Stamm gelebt hatten. Die späteren Nationen geführt durch die Bändiger entickelten die Sprachen weiter, die von Naitro'Nai wurde marziallischer, vorallem in der Hölle, als sich Bedeutungen start änderten.</t>
   </si>
@@ -315,9 +315,6 @@
     <t>Fire</t>
   </si>
   <si>
-    <t>Animal</t>
-  </si>
-  <si>
     <t>Body</t>
   </si>
   <si>
@@ -415,6 +412,15 @@
   </si>
   <si>
     <t>Wheat</t>
+  </si>
+  <si>
+    <t>Nel</t>
+  </si>
+  <si>
+    <t>Flora</t>
+  </si>
+  <si>
+    <t>Fauna</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1146,7 +1152,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
         <v>92</v>
@@ -1154,7 +1160,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
         <v>93</v>
@@ -1162,7 +1168,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s">
         <v>94</v>
@@ -1170,7 +1176,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s">
         <v>95</v>
@@ -1178,122 +1184,130 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" t="s">
         <v>128</v>
       </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>129</v>
+      </c>
+      <c r="B73" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
+++ b/docs/Buch Bayrische Nächte/Sprache der Seelenbändiger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Bayrische Nächte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C641AC3F-C8E7-4B03-B6E1-B292EEF31CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FB6789-0EB4-48B6-A99C-A0091210393B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -321,9 +321,6 @@
     <t>Metal</t>
   </si>
   <si>
-    <t>Steel</t>
-  </si>
-  <si>
     <t>Mind</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>Shi</t>
   </si>
   <si>
-    <t>Asht</t>
-  </si>
-  <si>
     <t>Rui</t>
   </si>
   <si>
@@ -421,6 +415,12 @@
   </si>
   <si>
     <t>Fauna</t>
+  </si>
+  <si>
+    <t>Ashmetal</t>
+  </si>
+  <si>
+    <t>Miasht</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
         <v>92</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B55" t="s">
         <v>93</v>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
         <v>94</v>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
         <v>95</v>
@@ -1184,15 +1184,15 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
         <v>96</v>
@@ -1200,114 +1200,114 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
